--- a/results.xlsx
+++ b/results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="545">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -34,145 +34,145 @@
     <t xml:space="preserve">Afghanistan</t>
   </si>
   <si>
-    <t xml:space="preserve">2948.442173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.921284</t>
+    <t xml:space="preserve">3300.521960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.973240</t>
   </si>
   <si>
     <t xml:space="preserve">Albania</t>
   </si>
   <si>
-    <t xml:space="preserve">22106.478891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.972372</t>
+    <t xml:space="preserve">23436.004534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.567210</t>
   </si>
   <si>
     <t xml:space="preserve">Algeria</t>
   </si>
   <si>
-    <t xml:space="preserve">32553.429212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.728463</t>
+    <t xml:space="preserve">36034.506143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">443.795631</t>
   </si>
   <si>
     <t xml:space="preserve">Angola</t>
   </si>
   <si>
-    <t xml:space="preserve">132549.005783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.726781</t>
+    <t xml:space="preserve">141384.983685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374.452066</t>
   </si>
   <si>
     <t xml:space="preserve">Antigua and Barbuda</t>
   </si>
   <si>
-    <t xml:space="preserve">14234.941308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335403</t>
+    <t xml:space="preserve">15225.942720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351941</t>
   </si>
   <si>
     <t xml:space="preserve">Argentina</t>
   </si>
   <si>
-    <t xml:space="preserve">53782.405601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.068926</t>
+    <t xml:space="preserve">56143.185803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.982597</t>
   </si>
   <si>
     <t xml:space="preserve">Armenia</t>
   </si>
   <si>
-    <t xml:space="preserve">94841.347110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.208813</t>
+    <t xml:space="preserve">101863.289874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.371285</t>
   </si>
   <si>
     <t xml:space="preserve">Australia</t>
   </si>
   <si>
-    <t xml:space="preserve">323755.871787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.979221</t>
+    <t xml:space="preserve">339634.043558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763.484985</t>
   </si>
   <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
-    <t xml:space="preserve">166217.980472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">876.692959</t>
+    <t xml:space="preserve">176394.655849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">895.357210</t>
   </si>
   <si>
     <t xml:space="preserve">Azerbaijan</t>
   </si>
   <si>
-    <t xml:space="preserve">78610.291198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.574826</t>
+    <t xml:space="preserve">81713.587003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.305174</t>
   </si>
   <si>
     <t xml:space="preserve">Bahamas</t>
   </si>
   <si>
-    <t xml:space="preserve">7801.679766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452010</t>
+    <t xml:space="preserve">8468.736423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474816</t>
   </si>
   <si>
     <t xml:space="preserve">Bahrain</t>
   </si>
   <si>
-    <t xml:space="preserve">161553.960763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.500018</t>
+    <t xml:space="preserve">171545.423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.737233</t>
   </si>
   <si>
     <t xml:space="preserve">Bangladesh</t>
   </si>
   <si>
-    <t xml:space="preserve">27646.551982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.864012</t>
+    <t xml:space="preserve">29173.138337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.546073</t>
   </si>
   <si>
     <t xml:space="preserve">Barbados</t>
   </si>
   <si>
-    <t xml:space="preserve">22149.049456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.822641</t>
+    <t xml:space="preserve">23476.093223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.877414</t>
   </si>
   <si>
     <t xml:space="preserve">Belarus</t>
   </si>
   <si>
-    <t xml:space="preserve">28541.382209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.447972</t>
+    <t xml:space="preserve">30379.539111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.019047</t>
   </si>
   <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
-    <t xml:space="preserve">437933.140204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9095.998834</t>
+    <t xml:space="preserve">457258.692912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9213.596600</t>
   </si>
   <si>
     <t xml:space="preserve">Belize</t>
@@ -181,43 +181,43 @@
     <t xml:space="preserve">4990.067241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253730</t>
+    <t xml:space="preserve">0.242923</t>
   </si>
   <si>
     <t xml:space="preserve">Benin</t>
   </si>
   <si>
-    <t xml:space="preserve">47847.192014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.565329</t>
+    <t xml:space="preserve">52334.445877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.451211</t>
   </si>
   <si>
     <t xml:space="preserve">Bhutan</t>
   </si>
   <si>
-    <t xml:space="preserve">41.972315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005061</t>
+    <t xml:space="preserve">63.946430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007384</t>
   </si>
   <si>
     <t xml:space="preserve">Bolivia (Plurinational State of)</t>
   </si>
   <si>
-    <t xml:space="preserve">13606.889600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.927145</t>
+    <t xml:space="preserve">14522.485388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.978246</t>
   </si>
   <si>
     <t xml:space="preserve">Bosnia and Herzegovina</t>
   </si>
   <si>
-    <t xml:space="preserve">125290.571427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.809978</t>
+    <t xml:space="preserve">133736.733763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.644342</t>
   </si>
   <si>
     <t xml:space="preserve">Botswana</t>
@@ -226,1369 +226,1381 @@
     <t xml:space="preserve">4082.800305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.216899</t>
+    <t xml:space="preserve">2.122480</t>
   </si>
   <si>
     <t xml:space="preserve">Brazil</t>
   </si>
   <si>
-    <t xml:space="preserve">82066.722925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">976.072199</t>
+    <t xml:space="preserve">88205.677505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1006.926370</t>
   </si>
   <si>
     <t xml:space="preserve">Bulgaria</t>
   </si>
   <si>
-    <t xml:space="preserve">198342.556011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713.114101</t>
+    <t xml:space="preserve">209798.091485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.548810</t>
   </si>
   <si>
     <t xml:space="preserve">Burkina Faso</t>
   </si>
   <si>
-    <t xml:space="preserve">48899.488534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.391791</t>
+    <t xml:space="preserve">53845.902289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.093955</t>
   </si>
   <si>
     <t xml:space="preserve">Burundi</t>
   </si>
   <si>
-    <t xml:space="preserve">6568.417952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893600</t>
+    <t xml:space="preserve">7160.511499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932812</t>
   </si>
   <si>
     <t xml:space="preserve">Cabo Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">22133.079883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.397633</t>
+    <t xml:space="preserve">24837.768240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.624527</t>
   </si>
   <si>
     <t xml:space="preserve">Cambodia</t>
   </si>
   <si>
-    <t xml:space="preserve">23362.559237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.848849</t>
+    <t xml:space="preserve">24719.155541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.187963</t>
   </si>
   <si>
     <t xml:space="preserve">Cameroon</t>
   </si>
   <si>
-    <t xml:space="preserve">26157.551072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.237802</t>
+    <t xml:space="preserve">29188.510556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.224080</t>
   </si>
   <si>
     <t xml:space="preserve">Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">494152.380476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5818.011532</t>
+    <t xml:space="preserve">515229.254770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5888.651777</t>
   </si>
   <si>
     <t xml:space="preserve">Central African Republic</t>
   </si>
   <si>
-    <t xml:space="preserve">8876.015685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499054</t>
+    <t xml:space="preserve">9573.191382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517622</t>
   </si>
   <si>
     <t xml:space="preserve">Chad</t>
   </si>
   <si>
-    <t xml:space="preserve">117.748383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000697</t>
+    <t xml:space="preserve">201.090115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001427</t>
   </si>
   <si>
     <t xml:space="preserve">Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">88376.610427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.108012</t>
+    <t xml:space="preserve">95055.423125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.610118</t>
   </si>
   <si>
     <t xml:space="preserve">China Hong Kong SAR</t>
   </si>
   <si>
-    <t xml:space="preserve">227364.808564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">454.282160</t>
+    <t xml:space="preserve">233585.465884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">449.296613</t>
   </si>
   <si>
     <t xml:space="preserve">China Macao SAR</t>
   </si>
   <si>
-    <t xml:space="preserve">34237.192373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.839317</t>
+    <t xml:space="preserve">36003.297174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.878541</t>
   </si>
   <si>
     <t xml:space="preserve">China Taiwan Province of</t>
   </si>
   <si>
-    <t xml:space="preserve">171462.491382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1710.763948</t>
+    <t xml:space="preserve">176603.263359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1688.508016</t>
   </si>
   <si>
     <t xml:space="preserve">China mainland</t>
   </si>
   <si>
-    <t xml:space="preserve">312342.033430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55528.309700</t>
+    <t xml:space="preserve">327555.795928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55776.939109</t>
   </si>
   <si>
     <t xml:space="preserve">Colombia</t>
   </si>
   <si>
-    <t xml:space="preserve">50004.568901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">481.059677</t>
+    <t xml:space="preserve">52263.153834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481.681503</t>
   </si>
   <si>
     <t xml:space="preserve">Comoros</t>
   </si>
   <si>
-    <t xml:space="preserve">2606.655066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022716</t>
+    <t xml:space="preserve">2933.616625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.025757</t>
   </si>
   <si>
     <t xml:space="preserve">Congo</t>
   </si>
   <si>
-    <t xml:space="preserve">34207.773452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.899220</t>
+    <t xml:space="preserve">37802.529243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.192987</t>
   </si>
   <si>
     <t xml:space="preserve">Costa Rica</t>
   </si>
   <si>
-    <t xml:space="preserve">41674.961141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.558425</t>
+    <t xml:space="preserve">43688.825456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.883503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cote d'Ivoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94712.993442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.935357</t>
   </si>
   <si>
     <t xml:space="preserve">Croatia</t>
   </si>
   <si>
-    <t xml:space="preserve">88533.007669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.861545</t>
+    <t xml:space="preserve">95260.942052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.244961</t>
   </si>
   <si>
     <t xml:space="preserve">Cuba</t>
   </si>
   <si>
-    <t xml:space="preserve">5452.135514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.120365</t>
+    <t xml:space="preserve">5982.832394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.537733</t>
   </si>
   <si>
     <t xml:space="preserve">Cyprus</t>
   </si>
   <si>
-    <t xml:space="preserve">91921.462241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.056825</t>
+    <t xml:space="preserve">98813.280022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.741446</t>
   </si>
   <si>
     <t xml:space="preserve">Czechia</t>
   </si>
   <si>
-    <t xml:space="preserve">171132.179169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520.363313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CГґte d'Ivoire</t>
+    <t xml:space="preserve">181503.356240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530.299845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35316.146224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.123795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215670.060248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.682294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Djibouti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52459.959247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.227621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8473.937808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominican Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57103.759366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.386374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33960.932123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.127381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160825.458637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3400.434543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Salvador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24827.701986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.761027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98831.055493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.641529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eswatini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9169.106351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.145521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethiopia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35456.050511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.362642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18451.755236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.632695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125085.020581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.077600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523032.656327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6739.812387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French Polynesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22109.928068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75851.428959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.042456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18465.740235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.402633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117408.794078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.526395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">594591.658534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19480.450775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59168.495372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.988820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287366.856666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1031.706851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9177.899738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guatemala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54604.535913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.288690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23367.588066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.579153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinea-Bissau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2299.893357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.051956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guyana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26278.913731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.253590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9157.272077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.705613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honduras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13264.623100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.047857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98677.450838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">497.310246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78886.504704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.160057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345489.064488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12276.498000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135072.381518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2306.997825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iran (Islamic Republic of)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26234.459912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.191472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iraq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64683.186696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">457.398405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227633.721947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">897.456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209542.873695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1023.432633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486171.477625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12703.753037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41713.804276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.195537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309012.065539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9845.637681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215640.550930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">767.909123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98037.190777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.561503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133642.616514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.325850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiribati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">696.972823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221440.230655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.858474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyrgyzstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43476.172766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.339135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lao People's Democratic Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1155.726478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.665699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125596.979904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245.622779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebanon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203977.012612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">425.365614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lesotho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.982207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35895.156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.800580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50102.180208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.985093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152079.199602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.141265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9915.693994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.309917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madagascar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19530.236207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.361365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4642.720105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">390829.080927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5446.399448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maldives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41614.520084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.377628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19310.977930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.635086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57204.205087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.308556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauritania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62188.254575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauritius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82146.999303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.512222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67323.267003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2107.404599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mongolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69293.212078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.736348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montenegro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50156.966215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.310827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171218.595879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2071.703710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myanmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21828.212793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.931665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namibia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34233.758003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.770721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nepal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24586.756588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.677601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands (Kingdom of the)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">644982.829919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23001.050468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Caledonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7167.339768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233683.654406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.397052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicaragua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14217.082680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.282600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43040.173290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.845393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37099.952446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.621415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Macedonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109643.462171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.181613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253023.045731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">666.871561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82172.568063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.730081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141031.857490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1742.935694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34233.784215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.810225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papua New Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2948.295587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.173458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13823.948325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.044002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45698.023672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.839363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108949.453087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1762.938663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245679.974520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2850.527503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246637.316770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1516.678819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187267.570407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.499704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198093.346382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4265.651177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Moldova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85153.338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.199352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166027.421443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1036.684600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russian Federation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130756.483732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.015135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rwanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35952.440811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.525714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Lucia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5488.298100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4089.858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.025462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sao Tome and Principe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4524.855145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142765.402230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2500.810272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203298.152419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">608.211184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165254.822656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.249332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seychelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24850.980535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95167.316189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.320797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181885.216288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.569779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solomon Islands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.846549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somalia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9164.999772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.232515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284326.273701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1372.011039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.522911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">428096.538638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12953.009857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri Lanka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45480.332186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.079637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15195.958232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.607236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suriname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37859.337731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.534079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293804.107130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">904.977290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417180.897822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1077.905192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syrian Arab Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17250.093829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.999280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tajikistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18388.511960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.427772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thailand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120224.719491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1057.865877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Togo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57179.556894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.244478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377.952000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76112.450372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.969088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88443.765236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361.075632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423654.323764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9851.066846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkmenistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5987.155429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.525030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuvalu</t>
   </si>
   <si>
     <t xml:space="preserve">0.000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Democratic Republic of the Congo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33529.248083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.593338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204002.972657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.231789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Djibouti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50180.530252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.162111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7806.936017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominican Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52350.741218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.584189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32278.762976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.791423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151252.482220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3304.004886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Salvador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23452.168959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.154427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91939.504974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.770119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eswatini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8466.370704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.031690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethiopia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33720.964509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.139309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17322.704461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.510105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121015.564959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.383029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501566.224203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6600.253376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French Polynesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20839.407751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70089.955720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.930838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16255.834079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.476972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109658.271415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.287631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">571443.391342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19225.427504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54131.784874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.244579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">273234.953878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1015.978584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8473.899628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.446465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guatemala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52274.544851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.038032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20762.937965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.452285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guinea-Bissau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1774.858717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.040936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guyana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24846.875925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.170640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8456.061360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.460654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honduras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12363.252979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.443521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91797.073211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">482.136380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iceland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72994.032764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.848265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331737.877033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12157.259311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126845.130270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2252.867909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iran (Islamic Republic of)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24801.923976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.436689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iraq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61841.756934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.653741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215551.754985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">885.721972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198098.420911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">977.375769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">465990.929387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12579.097753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamaica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39759.777638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.979870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294184.484313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9766.825795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203985.595969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">745.044953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91184.874379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.150969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kenya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125165.839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">611.137602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiribati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">696.972823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuwait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209576.939143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.852871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyrgyzstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39520.637640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.278058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lao People's Democratic Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">984.572171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117500.035003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">239.658091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebanon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192711.574708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370.008783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lesotho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.982207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liberia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32408.751689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.659110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45736.864072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.813382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142869.321643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.083079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9174.413913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.164682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madagascar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17233.751533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.421442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malawi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4220.930590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malaysia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">373380.585588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5348.094331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maldives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39658.283734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.320918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16927.394566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.323118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54787.987844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.210572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mauritania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57144.432492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.910759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mauritius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79064.213983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.366655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mexico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62036.912373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025.385379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mongolia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66493.461247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.452973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montenegro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47944.776764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.214342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161212.691591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023.864948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myanmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20643.954709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.210933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namibia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30874.976852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.834267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nepal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23237.255923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.856094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands (Kingdom of the)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">620642.287405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22678.047578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Caledonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6572.907373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221384.930358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">414.768572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicaragua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13274.111278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.914913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38988.713009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.234465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33572.411193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.177723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Macedonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102257.128903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.563643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240053.543607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">658.047472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76090.163095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.215828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pakistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136791.137605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1760.787417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32521.266395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.119720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papua New Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2623.411927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.018496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paraguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12910.767068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.968456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43631.047562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.867044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101662.610355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1715.849653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232897.724136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2798.930225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233879.263218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1494.555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qatar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181894.158041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.579945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187092.774796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4201.273177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Moldova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78925.689952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.805571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156252.078850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1007.404757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Russian Federation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121830.091817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.459145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rwanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34180.404487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.979429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saint Lucia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4991.443827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saint Vincent and the Grenadines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3682.856054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">469.995382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.021514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sao Tome and Principe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4088.669293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.084033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Arabia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133939.562908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2432.752784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senegal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192032.608511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">583.426869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155405.565752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.098536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seychelles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23471.926895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91762.828560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.309554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171497.405573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.959663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solomon Islands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.846549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somalia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8459.446025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.811777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270297.602726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1354.165497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Sudan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228.615578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409595.721823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12881.706447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Lanka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41389.779415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.887901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sudan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14204.339319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.238314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suriname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36027.398339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.372867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279455.768819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">891.868119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398916.574618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1058.412455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syrian Arab Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16039.183600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.050763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tajikistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17258.941878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.760399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thailand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116275.746855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1065.793175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Togo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52414.842962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.566926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377.952000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trinidad and Tobago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70338.168660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.161620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82048.428761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.804665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkmenistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5456.593053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.287760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuvalu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TГјrkiye</t>
-  </si>
-  <si>
     <t xml:space="preserve">Uganda</t>
   </si>
   <si>
-    <t xml:space="preserve">13080.729509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.661194</t>
+    <t xml:space="preserve">13989.717065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.062867</t>
   </si>
   <si>
     <t xml:space="preserve">Ukraine</t>
   </si>
   <si>
-    <t xml:space="preserve">199186.417454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.547063</t>
+    <t xml:space="preserve">214606.951120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">234.849215</t>
   </si>
   <si>
     <t xml:space="preserve">United Arab Emirates</t>
   </si>
   <si>
-    <t xml:space="preserve">447463.610405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4175.927469</t>
+    <t xml:space="preserve">467070.804862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4259.560600</t>
   </si>
   <si>
     <t xml:space="preserve">United Kingdom of Great Britain and Northern Ireland</t>
   </si>
   <si>
-    <t xml:space="preserve">639312.895131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10100.563186</t>
+    <t xml:space="preserve">664379.149454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10226.260866</t>
   </si>
   <si>
     <t xml:space="preserve">United Republic of Tanzania</t>
   </si>
   <si>
-    <t xml:space="preserve">43329.047205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.871358</t>
+    <t xml:space="preserve">47535.151723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.214505</t>
   </si>
   <si>
     <t xml:space="preserve">United States of America</t>
   </si>
   <si>
-    <t xml:space="preserve">623318.482880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23458.841989</t>
+    <t xml:space="preserve">648873.122115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24029.485858</t>
   </si>
   <si>
     <t xml:space="preserve">Uruguay</t>
   </si>
   <si>
-    <t xml:space="preserve">27672.185899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.996886</t>
+    <t xml:space="preserve">30800.202636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.370742</t>
   </si>
   <si>
     <t xml:space="preserve">Uzbekistan</t>
   </si>
   <si>
-    <t xml:space="preserve">54129.912812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">239.614069</t>
+    <t xml:space="preserve">58997.002092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.166189</t>
   </si>
   <si>
     <t xml:space="preserve">Vanuatu</t>
@@ -1597,52 +1609,52 @@
     <t xml:space="preserve">987.573002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.033599</t>
+    <t xml:space="preserve">0.032168</t>
   </si>
   <si>
     <t xml:space="preserve">Venezuela (Bolivarian Republic of)</t>
   </si>
   <si>
-    <t xml:space="preserve">16148.535332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.185614</t>
+    <t xml:space="preserve">17242.220840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.562377</t>
   </si>
   <si>
     <t xml:space="preserve">Viet Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">84959.513265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1606.997210</t>
+    <t xml:space="preserve">91508.646205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1677.599262</t>
   </si>
   <si>
     <t xml:space="preserve">Yemen</t>
   </si>
   <si>
-    <t xml:space="preserve">30849.930496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.356251</t>
+    <t xml:space="preserve">32509.109046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.788551</t>
   </si>
   <si>
     <t xml:space="preserve">Zambia</t>
   </si>
   <si>
-    <t xml:space="preserve">11528.313322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.980779</t>
+    <t xml:space="preserve">12341.023736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.040857</t>
   </si>
   <si>
     <t xml:space="preserve">Zimbabwe</t>
   </si>
   <si>
-    <t xml:space="preserve">10677.141933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.773660</t>
+    <t xml:space="preserve">11493.840145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.045809</t>
   </si>
 </sst>
 </file>
@@ -2366,1492 +2378,1492 @@
         <v>139</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>139</v>
+        <v>500</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>139</v>
+        <v>502</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>139</v>
+        <v>502</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
